--- a/templates/PlantillaReporte.xlsx
+++ b/templates/PlantillaReporte.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83AEBC84-BFF1-4B2D-8A80-F2D6B77D899C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4AE939D-A58C-4722-AE99-FBB61E74174E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>SOLICITUD DE RECIBO</t>
   </si>
   <si>
-    <t>FACTURACIÓN DE IGUALAS Y PAGOS EN PARCIALIDADES</t>
+    <t xml:space="preserve"> {texto_tipo}</t>
   </si>
   <si>
     <t>Fecha:</t>
@@ -478,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -527,6 +527,48 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
@@ -534,50 +576,6 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1014,30 +1012,30 @@
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" ht="23.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="35"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="38"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="1:9" ht="14.25">
       <c r="A8" s="4"/>
@@ -1091,11 +1089,11 @@
       <c r="B12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="6"/>
     </row>
@@ -1104,13 +1102,13 @@
       <c r="B13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6"/>
     </row>
@@ -1119,13 +1117,13 @@
       <c r="B14" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
       <c r="H14" s="7"/>
       <c r="I14" s="6"/>
     </row>
@@ -1134,13 +1132,13 @@
       <c r="B15" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="7"/>
       <c r="I15" s="6"/>
     </row>
@@ -1149,13 +1147,13 @@
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="7"/>
       <c r="I16" s="6"/>
     </row>
@@ -1164,13 +1162,13 @@
       <c r="B17" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
       <c r="H17" s="7"/>
       <c r="I17" s="6"/>
     </row>
@@ -1179,13 +1177,13 @@
       <c r="B18" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="7"/>
       <c r="I18" s="6"/>
     </row>
@@ -1328,13 +1326,13 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="4"/>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
       <c r="H29" s="5"/>
       <c r="I29" s="6"/>
     </row>
@@ -1343,11 +1341,11 @@
       <c r="B30" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="5"/>
       <c r="I30" s="6"/>
     </row>
@@ -1368,12 +1366,12 @@
         <v>32</v>
       </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
       <c r="H32" s="5"/>
       <c r="I32" s="6"/>
     </row>
@@ -1445,7 +1443,7 @@
       <c r="D38" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E38" s="49"/>
+      <c r="E38" s="47"/>
       <c r="F38" s="28"/>
       <c r="G38" s="28"/>
       <c r="H38" s="5"/>
@@ -1460,7 +1458,7 @@
       <c r="D39" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="49"/>
+      <c r="E39" s="47"/>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
       <c r="H39" s="5"/>
@@ -1475,7 +1473,7 @@
       <c r="D40" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="49"/>
+      <c r="E40" s="47"/>
       <c r="F40" s="28"/>
       <c r="G40" s="28"/>
       <c r="H40" s="5"/>
@@ -1496,10 +1494,10 @@
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="50" t="s">
+      <c r="D42" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="E42" s="50"/>
+      <c r="E42" s="48"/>
       <c r="F42" s="7"/>
       <c r="G42" s="16" t="s">
         <v>43</v>
@@ -1516,12 +1514,12 @@
       <c r="D43" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="49"/>
+      <c r="E43" s="47"/>
       <c r="F43" s="5"/>
       <c r="G43" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="49"/>
+      <c r="H43" s="47"/>
       <c r="I43" s="6"/>
       <c r="J43" s="26"/>
       <c r="K43" s="17"/>
@@ -1535,12 +1533,12 @@
       <c r="D44" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="49"/>
+      <c r="E44" s="47"/>
       <c r="F44" s="5"/>
       <c r="G44" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="H44" s="49"/>
+      <c r="H44" s="47"/>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:11">
@@ -1552,12 +1550,12 @@
       <c r="D45" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="49"/>
+      <c r="E45" s="47"/>
       <c r="F45" s="7"/>
       <c r="G45" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="H45" s="49"/>
+      <c r="H45" s="47"/>
       <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:11">
@@ -1569,72 +1567,72 @@
       <c r="D46" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="49"/>
+      <c r="E46" s="47"/>
       <c r="F46" s="7"/>
       <c r="G46" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="H46" s="49"/>
+      <c r="H46" s="47"/>
       <c r="I46" s="6"/>
     </row>
     <row r="47" spans="1:11" ht="41.25" customHeight="1">
       <c r="A47" s="4"/>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="C47" s="51"/>
+      <c r="C47" s="49"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="H47" s="51"/>
+      <c r="H47" s="49"/>
       <c r="I47" s="6"/>
     </row>
     <row r="48" spans="1:11" ht="14.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="52" t="s">
+      <c r="B48" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="52"/>
+      <c r="C48" s="50"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
-      <c r="G48" s="52" t="s">
+      <c r="G48" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="H48" s="52"/>
+      <c r="H48" s="50"/>
       <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" ht="22.5" customHeight="1">
       <c r="A49" s="4"/>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="53"/>
+      <c r="C49" s="51"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
-      <c r="G49" s="32" t="s">
+      <c r="G49" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="53"/>
+      <c r="H49" s="51"/>
       <c r="I49" s="6"/>
     </row>
     <row r="50" spans="1:9" ht="14.25">
       <c r="A50" s="4"/>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="C50" s="54"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="54" t="s">
+      <c r="G50" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="H50" s="54"/>
+      <c r="H50" s="52"/>
       <c r="I50" s="6"/>
     </row>
     <row r="51" spans="1:9">
@@ -1664,6 +1662,20 @@
     <row r="68" ht="14.25"/>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A7:I7"/>
@@ -1680,20 +1692,6 @@
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D40:E40"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="G49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/templates/PlantillaReporte.xlsx
+++ b/templates/PlantillaReporte.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4AE939D-A58C-4722-AE99-FBB61E74174E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02BD88F9-F43B-47C5-92AC-3FBE21E3D2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -606,15 +606,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
+      <xdr:colOff>371475</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -637,8 +637,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="276225" y="247650"/>
-          <a:ext cx="3171825" cy="552450"/>
+          <a:off x="371475" y="238125"/>
+          <a:ext cx="2047875" cy="733425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
